--- a/artfynd/A 19845-2026 artfynd.xlsx
+++ b/artfynd/A 19845-2026 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>134243105</v>
       </c>
       <c r="B5" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>134243073</v>
       </c>
       <c r="B6" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>134243109</v>
       </c>
       <c r="B7" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>134243085</v>
       </c>
       <c r="B9" t="n">
-        <v>98043</v>
+        <v>98045</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>134243071</v>
       </c>
       <c r="B10" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>134243076</v>
       </c>
       <c r="B12" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>134243092</v>
       </c>
       <c r="B14" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>134243064</v>
       </c>
       <c r="B21" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>134243104</v>
       </c>
       <c r="B22" t="n">
-        <v>92228</v>
+        <v>92230</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>134243087</v>
       </c>
       <c r="B23" t="n">
-        <v>92228</v>
+        <v>92230</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>134243107</v>
       </c>
       <c r="B25" t="n">
-        <v>101288</v>
+        <v>101290</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>134243103</v>
       </c>
       <c r="B26" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>134243069</v>
       </c>
       <c r="B27" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>134243106</v>
       </c>
       <c r="B28" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>134243102</v>
       </c>
       <c r="B29" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>134243080</v>
       </c>
       <c r="B30" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>134243089</v>
       </c>
       <c r="B32" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>134243100</v>
       </c>
       <c r="B33" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>134243081</v>
       </c>
       <c r="B35" t="n">
-        <v>92349</v>
+        <v>92351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>134243093</v>
       </c>
       <c r="B36" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>134243065</v>
       </c>
       <c r="B37" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 19845-2026 artfynd.xlsx
+++ b/artfynd/A 19845-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243087</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243104</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243111</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243080</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243103</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243109</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243073</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243076</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1648,6 +1693,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243066</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1768,6 +1818,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243072</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1888,6 +1943,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243074</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2008,6 +2068,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243075</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2128,6 +2193,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243077</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2248,6 +2318,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243079</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2368,6 +2443,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243082</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2488,6 +2568,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243084</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2608,6 +2693,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243086</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2728,6 +2818,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243088</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2848,6 +2943,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243091</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2968,6 +3068,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243094</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3088,6 +3193,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243095</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3208,6 +3318,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243096</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3328,6 +3443,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243097</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3448,6 +3568,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243098</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3568,6 +3693,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243099</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3688,6 +3818,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243110</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3808,6 +3943,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243112</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3920,6 +4060,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243063</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4032,6 +4177,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243064</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4144,6 +4294,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243065</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4256,6 +4411,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243068</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4368,6 +4528,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243069</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4480,6 +4645,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243071</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4592,6 +4762,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243089</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4704,6 +4879,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243092</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4816,6 +4996,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243093</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4928,6 +5113,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243100</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5040,6 +5230,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243101</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5152,6 +5347,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243102</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5264,6 +5464,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243105</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5376,6 +5581,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243106</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5483,6 +5693,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243085</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5590,6 +5805,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243107</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5698,8 +5918,59 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134243081</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>